--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_322_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_322_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8409</v>
+        <v>5.8243</v>
       </c>
       <c r="E2" t="n">
-        <v>7.923</v>
+        <v>8.4695</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0821</v>
+        <v>-2.6452</v>
       </c>
       <c r="G2" t="n">
         <v>4.6651</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6311</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7389</v>
+        <v>-0.1924</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8922</v>
+        <v>-0.4553</v>
       </c>
       <c r="V2" t="n">
         <v>3.8945</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0705</v>
+        <v>2.6062</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6419</v>
+        <v>1.2447</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4286</v>
+        <v>1.3614</v>
       </c>
       <c r="G3" t="n">
         <v>0.9071</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.5329</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5702</v>
+        <v>0.1731</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6387</v>
+        <v>-0.7059</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.066</v>
+        <v>1.3938</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7781</v>
+        <v>3.2066</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.712</v>
+        <v>-1.8129</v>
       </c>
       <c r="G4" t="n">
         <v>2.987</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7279</v>
+        <v>-0.4002</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4402</v>
+        <v>-0.0116</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2877</v>
+        <v>-0.3886</v>
       </c>
       <c r="V4" t="n">
         <v>2.2862</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6973</v>
+        <v>0.9937</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7326</v>
+        <v>-0.0955</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0353</v>
+        <v>1.0892</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3106</v>
+        <v>0.3629</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2448</v>
+        <v>0.3494</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5553</v>
+        <v>0.0134</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1624</v>
+        <v>0.0341</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1344</v>
+        <v>-0.6652</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0279</v>
+        <v>0.6993</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8518</v>
+        <v>0.3288</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3792</v>
+        <v>1.0146</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4726</v>
+        <v>-0.6859</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7631</v>
+        <v>-0.297</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5702</v>
+        <v>-0.1296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1929</v>
+        <v>-0.1674</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6159</v>
+        <v>0.3008</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4061</v>
+        <v>3.5714</v>
       </c>
       <c r="F6" t="n">
-        <v>1.022</v>
+        <v>-3.2705</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3629</v>
+        <v>0.3106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3494</v>
+        <v>-0.2448</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0134</v>
+        <v>0.5553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0341</v>
+        <v>3.1624</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6652</v>
+        <v>0.1344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6993</v>
+        <v>3.0279</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3288</v>
+        <v>-2.8518</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0146</v>
+        <v>-0.3792</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6859</v>
+        <v>-2.4726</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6748</v>
+        <v>0.3666</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4402</v>
+        <v>0.409</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2346</v>
+        <v>-0.0424</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1347</v>
+        <v>-0.0097</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0325</v>
+        <v>2.0807</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1672</v>
+        <v>-2.0903</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4185</v>
+        <v>2.5504</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6494</v>
+        <v>1.58</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2309</v>
+        <v>0.9704</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1072</v>
+        <v>2.1788</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0336</v>
+        <v>0.8907</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0736</v>
+        <v>1.2882</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5256999999999999</v>
+        <v>0.3715</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.6893</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>-0.3178</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0518</v>
+        <v>-0.8975</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0747</v>
+        <v>-0.0982</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1265</v>
+        <v>-0.7993</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3031</v>
+        <v>-0.1512</v>
       </c>
       <c r="E8" t="n">
-        <v>1.888</v>
+        <v>0.1505</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1911</v>
+        <v>-0.3017</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5504</v>
+        <v>-0.4185</v>
       </c>
       <c r="H8" t="n">
-        <v>1.58</v>
+        <v>-0.6494</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9704</v>
+        <v>0.2309</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1788</v>
+        <v>0.1072</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8907</v>
+        <v>0.0336</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2882</v>
+        <v>0.0736</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3715</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6893</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3178</v>
+        <v>0.1573</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1909</v>
+        <v>0.0354</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>0.0433</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3621</v>
+        <v>-1.9108</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1288</v>
+        <v>1.6137</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4909</v>
+        <v>-3.5245</v>
       </c>
       <c r="G9" t="n">
         <v>-5.0464</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4677</v>
+        <v>0.919</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9831</v>
+        <v>0.4681</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4846</v>
+        <v>0.4509</v>
       </c>
       <c r="V9" t="n">
         <v>2.6805</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4902</v>
+        <v>-6.0725</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0985</v>
+        <v>-0.4166</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.5887</v>
+        <v>-5.6559</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3816</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3706</v>
+        <v>0.7883</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9085</v>
+        <v>0.3934</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4621</v>
+        <v>0.3949</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6451</v>
+        <v>-6.8723</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2886</v>
+        <v>-0.5495</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.3564</v>
+        <v>-6.3228</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3658</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5988</v>
+        <v>0.174</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.731</v>
+        <v>0.0081</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1322</v>
+        <v>0.1658</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6805</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.644599999999998</v>
+        <v>-3.897699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>18.5287</v>
+        <v>19.2755</v>
       </c>
       <c r="F12" t="n">
-        <v>-23.1731</v>
+        <v>-23.1732</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4292000000000011</v>
+        <v>-0.4292000000000002</v>
       </c>
       <c r="H12" t="n">
         <v>1.4109</v>
@@ -1387,16 +1387,16 @@
         <v>-15.0769</v>
       </c>
       <c r="R12" t="n">
-        <v>9.2784</v>
+        <v>9.278400000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2388</v>
+        <v>-0.4919999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3161999999999999</v>
+        <v>1.0632</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.555</v>
+        <v>-1.5552</v>
       </c>
       <c r="V12" t="n">
         <v>2.8223</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5937</v>
+        <v>6.3293</v>
       </c>
       <c r="E13" t="n">
-        <v>8.6296</v>
+        <v>8.983499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0359</v>
+        <v>-2.6542</v>
       </c>
       <c r="G13" t="n">
         <v>5.2401</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.288</v>
+        <v>-0.5524</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9709</v>
+        <v>-0.617</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3172</v>
+        <v>0.0646</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6778999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5396</v>
+        <v>4.2359</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8358</v>
+        <v>6.3076</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2961</v>
+        <v>-2.0716</v>
       </c>
       <c r="G14" t="n">
         <v>3.7296</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8162</v>
+        <v>-0.1199</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5975</v>
+        <v>-0.1256</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2188</v>
+        <v>0.0057</v>
       </c>
       <c r="V14" t="n">
         <v>0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.699</v>
+        <v>3.2824</v>
       </c>
       <c r="E15" t="n">
         <v>2.8902</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1912</v>
+        <v>0.3922</v>
       </c>
       <c r="G15" t="n">
         <v>0.4342</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5755</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3339</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2416</v>
+        <v>0.3418</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2714</v>
+        <v>1.7489</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5576</v>
+        <v>2.9114</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2862</v>
+        <v>-1.1625</v>
       </c>
       <c r="G16" t="n">
         <v>0.446</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5689</v>
+        <v>-0.0914</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.2937</v>
       </c>
       <c r="V16" t="n">
         <v>0.9304</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2451</v>
+        <v>1.5774</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3036</v>
+        <v>2.6575</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0585</v>
+        <v>-1.0801</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1437</v>
@@ -1780,13 +1780,13 @@
         <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1415</v>
+        <v>0.4738</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1019</v>
+        <v>0.2519</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2434</v>
+        <v>0.2219</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5306999999999999</v>
+        <v>-0.5881</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4233</v>
+        <v>1.1969</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.8926</v>
+        <v>-1.785</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4227</v>
+        <v>2.1445</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7718</v>
+        <v>-0.0203</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1945</v>
+        <v>2.1648</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8826</v>
+        <v>2.4627</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1833</v>
+        <v>0.0336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6993</v>
+        <v>2.4291</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3053</v>
+        <v>-0.3182</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4116</v>
+        <v>-0.0539</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8938</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6545</v>
+        <v>-0.1966</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4169</v>
+        <v>-0.1061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2377</v>
+        <v>-0.0905</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.933</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.2166</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9978</v>
+        <v>-1.6279</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0789</v>
+        <v>-0.574</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0767</v>
+        <v>-1.0539</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1445</v>
+        <v>-2.3455</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0203</v>
+        <v>-1.2413</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1648</v>
+        <v>-1.1041</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4627</v>
+        <v>-0.7156</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0336</v>
+        <v>-0.7156</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4291</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3182</v>
+        <v>-1.6299</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0539</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2643</v>
+        <v>-1.1041</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6062</v>
+        <v>0.4856</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>0.3736</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3822</v>
+        <v>0.112</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.445</v>
+        <v>-1.6974</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5436</v>
+        <v>-1.678</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1467</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8461</v>
+        <v>0.5937</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5623</v>
+        <v>0.4443</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2838</v>
+        <v>0.1494</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6083</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2849</v>
+        <v>-1.9963</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1637</v>
+        <v>2.0643</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1211</v>
+        <v>-4.0606</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3455</v>
+        <v>-0.4227</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2413</v>
+        <v>0.7718</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1041</v>
+        <v>-1.1945</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7156</v>
+        <v>1.8826</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7156</v>
+        <v>1.1833</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6993</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6299</v>
+        <v>-2.3053</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.4116</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1041</v>
+        <v>-1.8938</v>
       </c>
       <c r="P21" t="n">
         <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1713</v>
+        <v>1.1275</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2161</v>
+        <v>1.0578</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0448</v>
+        <v>0.0696</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.933</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6984</v>
+        <v>-2.2641</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4379</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2606</v>
+        <v>-1.5751</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5898</v>
+        <v>-2.9168</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0673</v>
+        <v>-1.9231</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5224</v>
+        <v>-0.9937</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.8429</v>
+        <v>0.3142</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0565</v>
+        <v>-0.8501</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7863</v>
+        <v>1.1643</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7469</v>
+        <v>-3.231</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0108</v>
+        <v>-1.073</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7361</v>
+        <v>-2.1581</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6594</v>
+        <v>0.5083</v>
       </c>
       <c r="T22" t="n">
-        <v>0.637</v>
+        <v>0.476</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0224</v>
+        <v>0.0323</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8089</v>
+        <v>-2.7828</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0429</v>
+        <v>-2.5558</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.766</v>
+        <v>-0.227</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9168</v>
+        <v>-3.5898</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9231</v>
+        <v>-2.0673</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9937</v>
+        <v>-1.5224</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3142</v>
+        <v>-2.8429</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8501</v>
+        <v>-2.0565</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1643</v>
+        <v>-0.7863</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.231</v>
+        <v>-0.7469</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.073</v>
+        <v>-0.0108</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1581</v>
+        <v>-0.7361</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0365</v>
+        <v>0.575</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1221</v>
+        <v>0.519</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1586</v>
+        <v>0.056</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.644500000000001</v>
+        <v>6.2173</v>
       </c>
       <c r="E24" t="n">
-        <v>23.1731</v>
+        <v>23.1732</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.5285</v>
+        <v>-16.9558</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4292000000000007</v>
+        <v>0.4292000000000002</v>
       </c>
       <c r="H24" t="n">
         <v>-1.410900000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8403</v>
+        <v>1.840300000000001</v>
       </c>
       <c r="J24" t="n">
         <v>21.4988</v>
@@ -2317,25 +2317,25 @@
         <v>-16.8461</v>
       </c>
       <c r="P24" t="n">
-        <v>5.799000000000001</v>
+        <v>5.799</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.2784</v>
+        <v>-9.278399999999998</v>
       </c>
       <c r="R24" t="n">
         <v>15.077</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2389</v>
+        <v>2.8115</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5551</v>
+        <v>1.5549</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3163</v>
+        <v>1.2565</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8223</v>
+        <v>-2.822299999999999</v>
       </c>
       <c r="W24" t="n">
         <v>9.3973</v>
